--- a/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
+++ b/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
@@ -39,7 +39,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,11 +71,6 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -103,7 +98,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A87"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
@@ -690,7 +684,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  caution 924 | avoid 24 | good 989</t>
+          <t xml:space="preserve">  caution 925 | avoid 24 | good 988</t>
         </is>
       </c>
     </row>
@@ -705,7 +699,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Exceptions: 18 (14 stricter, 4 looser)</t>
+          <t xml:space="preserve">  Exceptions: 19 (15 stricter, 4 looser)</t>
         </is>
       </c>
     </row>
@@ -734,7 +728,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    declaration: 804</t>
+          <t xml:space="preserve">    declaration: 803</t>
         </is>
       </c>
     </row>
@@ -748,7 +742,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    exception: 18</t>
+          <t xml:space="preserve">    exception: 19</t>
         </is>
       </c>
     </row>
@@ -930,55 +924,6 @@
       <c r="A80" t="inlineStr">
         <is>
           <t xml:space="preserve">     condition.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. The Traps -&gt; neck muscle rule is INERT. "Traps" is in the authored</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     muscle vocabulary but is never a PRIMARY muscle on any strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     exercise, so the rule can never fire. Shrugs — the most neck-loading</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     lift in the pool — has primary "Upper back" and pattern</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     isolation_upper, so it matches no neck rule and lands on good via the</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     declaration. Recorded, flagged, and awaiting Sam. This is the same</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     failure mode as pubalgia: authored, and unreachable.</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3911,6 +3856,33 @@
         </is>
       </c>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>stricter</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Shrugs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>stricter</t>
         </is>
@@ -5680,7 +5652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5870,84 +5842,67 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>PART B — DUAL-TARGET routes. RULED BY SAM, BLOCKED IN THE MECHANISM.</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>hip flexor</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>hip</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ruled — single target, implementable</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>resolveInjuryBucket returns InjuryBucket | null — ONE bucket. The scalar is threaded through coachInjuryTargetResolver, programAdjustmentEngine, trainAroundEngine, injuryAdjustmentEngine and guidedInjuryControl. Recorded, NOT implemented, per Sam's own stop condition.</t>
+          <t>achilles</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>calf</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ruled — single target, implementable</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Athlete types…</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>RULED regions</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>upper back</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>shoulder</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ruled — single target, implementable</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>hip flexor</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>hip + quad</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BLOCKED — resolver is single-target</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>PART B — DUAL-TARGET routes: NONE. Ruled out by Sam, 2026-07-28.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>achilles</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>calf + ankle/foot</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BLOCKED — resolver is single-target</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>upper back</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>shoulder + neck</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>BLOCKED — resolver is single-target</t>
+          <t>Routing is SINGLE-TARGET everywhere: hip flexor -&gt; hip, achilles -&gt; calf, upper back -&gt; shoulder. Episode-identity semantics (bucket equality in coachInjuryTargetResolver) therefore stay untouched. Logged as a possible future refinement ONLY if athlete complaints expose coverage gaps.</t>
         </is>
       </c>
     </row>
@@ -15174,9 +15129,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M116" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="M116" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="N116" s="4" t="inlineStr">

--- a/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
+++ b/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
@@ -684,7 +684,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  caution 925 | avoid 24 | good 988</t>
+          <t xml:space="preserve">  caution 947 | avoid 24 | good 966</t>
         </is>
       </c>
     </row>
@@ -692,14 +692,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rules: 157 (20 authored by Sam for the new regions)</t>
+          <t xml:space="preserve">  Rules: 159 (22 authored by Sam for the new regions)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Exceptions: 19 (15 stricter, 4 looser)</t>
+          <t xml:space="preserve">  Exceptions: 21 (17 stricter, 4 looser)</t>
         </is>
       </c>
     </row>
@@ -721,14 +721,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    rule: 1020</t>
+          <t xml:space="preserve">    rule: 1040</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    declaration: 803</t>
+          <t xml:space="preserve">    declaration: 781</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    exception: 19</t>
+          <t xml:space="preserve">    exception: 21</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ONLY 33 OF THE 157 RULES CURRENTLY BIND.</t>
+          <t>ONLY 35 OF THE 159 RULES CURRENTLY BIND.</t>
         </is>
       </c>
     </row>
@@ -1404,9 +1404,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>caution ·Sam</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -1929,9 +1929,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>caution ·Sam</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -3317,7 +3317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3883,6 +3883,60 @@
         </is>
       </c>
       <c r="E23" t="inlineStr">
+        <is>
+          <t>stricter</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chest Supported Row</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ribs</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>stricter</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chest-Supported DB Row</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ribs</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>stricter</t>
         </is>
@@ -10199,9 +10253,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
@@ -10281,9 +10335,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
@@ -10363,9 +10417,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -10445,9 +10499,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -10527,9 +10581,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
@@ -10609,9 +10663,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
@@ -10691,9 +10745,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
@@ -10773,9 +10827,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -10855,9 +10909,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
@@ -10937,9 +10991,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -11101,9 +11155,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -11183,9 +11237,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -11265,9 +11319,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -11347,9 +11401,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -11429,9 +11483,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -11511,9 +11565,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -11593,9 +11647,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -11757,9 +11811,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -11839,9 +11893,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -12741,9 +12795,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K87" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L87" s="5" t="inlineStr">
@@ -12823,9 +12877,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K88" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L88" s="5" t="inlineStr">
@@ -12905,9 +12959,9 @@
           <t>good</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">

--- a/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
+++ b/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
@@ -684,7 +684,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  caution 871 | avoid 24 | good 1042</t>
+          <t xml:space="preserve">  caution 872 | avoid 24 | good 1041</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Exceptions: 23 (19 stricter, 4 looser)</t>
+          <t xml:space="preserve">  Exceptions: 24 (20 stricter, 4 looser)</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    declaration: 1039</t>
+          <t xml:space="preserve">    declaration: 1038</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    exception: 23</t>
+          <t xml:space="preserve">    exception: 24</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3991,6 +3991,33 @@
         </is>
       </c>
       <c r="E27" t="inlineStr">
+        <is>
+          <t>stricter</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Incline Y Raise</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ribs</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>stricter</t>
         </is>
@@ -15391,9 +15418,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K118" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">

--- a/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
+++ b/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
@@ -483,7 +483,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -505,7 +504,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
@@ -520,7 +518,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -549,7 +546,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -585,7 +581,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -607,7 +602,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -622,7 +616,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
@@ -651,7 +644,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -666,7 +658,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -688,7 +679,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -710,7 +700,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
@@ -760,7 +749,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
@@ -803,7 +791,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
@@ -832,7 +819,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -847,7 +833,6 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
@@ -869,7 +854,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -891,7 +875,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
@@ -3317,7 +3300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3459,76 +3442,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deadlift</t>
+          <t>Front Squat</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lowerBack</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>avoid</t>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>stricter</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sam, 2026-08-26: rack-position squats match Back Squat's shoulder caution — 'remove it from good'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trap Bar Deadlift</t>
+          <t>Box Squat</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>groin</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>caution</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>looser</t>
+          <t>stricter</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RDLs</t>
+          <t>High Box Squat</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hamstring</t>
+          <t>shoulder</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>avoid</t>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3540,12 +3528,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nordic Lower</t>
+          <t>Deadlift</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hamstring</t>
+          <t>lowerBack</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3567,7 +3555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lateral Bounds</t>
+          <t>Trap Bar Deadlift</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3577,29 +3565,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
           <t>avoid</t>
         </is>
       </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stricter</t>
+          <t>looser</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>RDLs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>groin</t>
+          <t>hamstring</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3621,7 +3609,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Nordic Lower</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3648,12 +3636,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Lateral Bounds</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>knee</t>
+          <t>groin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3680,7 +3668,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>calf</t>
+          <t>groin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3707,7 +3695,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ankle/foot</t>
+          <t>hamstring</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3729,7 +3717,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Depth Jumps</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3756,12 +3744,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Depth Jumps</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ankle/foot</t>
+          <t>calf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3783,12 +3771,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Scap Pull Ups</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lowerBack</t>
+          <t>ankle/foot</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3796,26 +3784,26 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>good</t>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>avoid</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>looser</t>
+          <t>stricter</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Scap Pull Ups</t>
+          <t>Depth Jumps</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>elbow</t>
+          <t>knee</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3823,26 +3811,26 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>good</t>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>avoid</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>looser</t>
+          <t>stricter</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Scap Pull Ups</t>
+          <t>Depth Jumps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wrist/hand</t>
+          <t>ankle/foot</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3850,26 +3838,26 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>good</t>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>avoid</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>looser</t>
+          <t>stricter</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ab Wheel</t>
+          <t>Scap Pull Ups</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>groin</t>
+          <t>lowerBack</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3877,26 +3865,26 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>avoid</t>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>good</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>stricter</t>
+          <t>looser</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dragon Flag</t>
+          <t>Scap Pull Ups</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>lowerBack</t>
+          <t>elbow</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3904,63 +3892,63 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>avoid</t>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>good</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>stricter</t>
+          <t>looser</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shrugs</t>
+          <t>Scap Pull Ups</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>neck</t>
+          <t>wrist/hand</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>caution</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>good</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stricter</t>
+          <t>looser</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chest Supported Row</t>
+          <t>Ab Wheel</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ribs</t>
+          <t>groin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>caution</t>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>avoid</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3972,22 +3960,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chest-Supported DB Row</t>
+          <t>Dragon Flag</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ribs</t>
+          <t>lowerBack</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>caution</t>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>avoid</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3999,25 +3987,106 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Shrugs</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>neck</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>stricter</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chest Supported Row</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ribs</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>stricter</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chest-Supported DB Row</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ribs</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>stricter</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Incline Y Raise</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>ribs</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>stricter</t>
         </is>
@@ -6333,7 +6402,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>good (dec)</t>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -6415,7 +6484,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>good (dec)</t>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -6661,7 +6730,7 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>good (dec)</t>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">

--- a/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
+++ b/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
@@ -3300,7 +3300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4089,6 +4089,198 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>stricter</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Leg Press</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>hamstring</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>looser</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Sam, 2026-08-27 (hamstring over-restriction fix): Bible hamstring section — 'Usually okay: non-painful quad-dominant lower work'; good swaps include box squat, controlled squat, step-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Box Squat</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>hamstring</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>looser</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Sam, 2026-08-27 (hamstring over-restriction fix): Bible hamstring section — 'Usually okay: non-painful quad-dominant lower work'; good swaps include box squat, controlled squat, step-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>High Box Squat</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>hamstring</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>looser</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Sam, 2026-08-27 (hamstring over-restriction fix): Bible hamstring section — 'Usually okay: non-painful quad-dominant lower work'; good swaps include box squat, controlled squat, step-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Goblet Squat</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>hamstring</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>looser</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sam, 2026-08-27 (hamstring over-restriction fix): Bible hamstring section — 'Usually okay: non-painful quad-dominant lower work'; good swaps include box squat, controlled squat, step-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Step Ups</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>hamstring</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>looser</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sam, 2026-08-27 (hamstring over-restriction fix): Bible hamstring section — 'Usually okay: non-painful quad-dominant lower work'; good swaps include box squat, controlled squat, step-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Leg Extension</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>hamstring</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>looser</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sam, 2026-08-27 (hamstring over-restriction fix): Bible hamstring section — 'Usually okay: non-painful quad-dominant lower work'; good swaps include box squat, controlled squat, step-up.</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6641,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -6531,7 +6723,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -6695,7 +6887,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -7023,7 +7215,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -7433,7 +7625,7 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -8417,7 +8609,7 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">

--- a/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
+++ b/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
@@ -483,7 +483,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -505,7 +504,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
@@ -520,7 +518,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -549,7 +546,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -585,7 +581,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -607,7 +602,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
@@ -622,7 +616,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
@@ -651,7 +644,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -666,7 +658,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -688,7 +679,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
@@ -710,7 +700,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
@@ -767,7 +756,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -817,7 +805,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
@@ -860,7 +847,6 @@
         </is>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
@@ -889,7 +875,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
@@ -904,7 +889,6 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
@@ -926,7 +910,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -948,7 +931,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
@@ -14970,7 +14952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P205"/>
+  <dimension ref="A1:P206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -16749,7 +16731,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hip Thrusts</t>
+          <t>B-Stance RDL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -16757,67 +16739,67 @@
           <t>hinge</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N26" s="10" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>avoid</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="O26" s="10" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="P26" s="10" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
@@ -16831,7 +16813,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Glute Bridge</t>
+          <t>Hip Thrusts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -16889,19 +16871,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -16913,12 +16895,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Single-Leg Hip Thrust</t>
+          <t>Glute Bridge</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
+          <t>hinge</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -16931,9 +16913,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -16956,9 +16938,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -16971,19 +16953,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="O28" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P28" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16977,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Back Extension</t>
+          <t>Single-Leg Hip Thrust</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -17003,9 +16985,9 @@
           <t>isolation_lower</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>avoid</t>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -17077,7 +17059,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nordic Lower</t>
+          <t>Back Extension</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -17085,9 +17067,9 @@
           <t>isolation_lower</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>avoid</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -17100,9 +17082,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -17135,19 +17117,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O30" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P30" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -17159,12 +17141,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kettlebell Swings</t>
+          <t>Nordic Lower</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>hinge</t>
+          <t>isolation_lower</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -17177,14 +17159,14 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -17202,9 +17184,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -17217,36 +17199,36 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N31" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="O31" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P31" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LOWER BODY — ISOLATION (rehab / prehab / tissue work)</t>
+          <t>LOWER BODY — HINGE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Leg Extension</t>
+          <t>Kettlebell Swings</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
+          <t>hinge</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -17259,14 +17241,14 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -17284,9 +17266,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -17299,19 +17281,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P32" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -17323,7 +17305,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Calf Raises</t>
+          <t>Leg Extension</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -17346,9 +17328,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -17405,7 +17387,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tib Raises</t>
+          <t>Calf Raises</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -17487,7 +17469,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Single-Leg Calf Raise</t>
+          <t>Tib Raises</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -17569,7 +17551,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Seated Calf Raise</t>
+          <t>Single-Leg Calf Raise</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -17651,7 +17633,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Groin Squeeze</t>
+          <t>Seated Calf Raise</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -17733,7 +17715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Banded TKE</t>
+          <t>Groin Squeeze</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -17815,7 +17797,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Spanish Squat Hold</t>
+          <t>Banded TKE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -17897,7 +17879,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Copenhagen Plank (Half)</t>
+          <t>Spanish Squat Hold</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -17955,14 +17937,14 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N40" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="O40" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -17979,7 +17961,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Long-Lever Copenhagen</t>
+          <t>Copenhagen Plank (Half)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -18061,7 +18043,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hamstring Curl</t>
+          <t>Long-Lever Copenhagen</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -18119,14 +18101,14 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="O42" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
@@ -18143,7 +18125,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Crab Walks</t>
+          <t>Hamstring Curl</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -18225,7 +18207,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Swiss Ball Hamstring Curl</t>
+          <t>Crab Walks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -18307,7 +18289,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bosch Hold</t>
+          <t>Swiss Ball Hamstring Curl</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -18384,17 +18366,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LOWER BODY — POWER / PLYO</t>
+          <t>LOWER BODY — ISOLATION (rehab / prehab / tissue work)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vertical Jump</t>
+          <t>Bosch Hold</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>plyo</t>
+          <t>isolation_lower</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -18432,9 +18414,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
@@ -18471,7 +18453,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pogo Hops</t>
+          <t>Vertical Jump</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -18553,7 +18535,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kneeling Jump</t>
+          <t>Pogo Hops</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -18635,7 +18617,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lateral Jump</t>
+          <t>Kneeling Jump</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -18717,7 +18699,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Box Jumps</t>
+          <t>Lateral Jump</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -18799,7 +18781,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Broad Jumps</t>
+          <t>Box Jumps</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -18881,7 +18863,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jump Squats</t>
+          <t>Broad Jumps</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -18963,7 +18945,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lateral Bounds</t>
+          <t>Jump Squats</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -18971,9 +18953,9 @@
           <t>plyo</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -19045,7 +19027,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RFE Split Squat Jump</t>
+          <t>Lateral Bounds</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -19068,24 +19050,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
@@ -19127,7 +19109,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Depth Jumps</t>
+          <t>RFE Split Squat Jump</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -19135,9 +19117,9 @@
           <t>plyo</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -19150,9 +19132,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -19160,9 +19142,9 @@
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="J55" s="9" t="inlineStr">
@@ -19204,52 +19186,52 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>UPPER BODY — HORIZONTAL PUSH</t>
+          <t>LOWER BODY — POWER / PLYO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bench Press</t>
+          <t>Depth Jumps</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>horizontal_push</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>plyo</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
@@ -19257,9 +19239,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
@@ -19267,19 +19249,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N56" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="O56" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="P56" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -19291,7 +19273,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DB Bench Press</t>
+          <t>Bench Press</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -19373,7 +19355,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Incline Bench</t>
+          <t>DB Bench Press</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -19421,9 +19403,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="L58" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
@@ -19455,7 +19437,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Incline DB Bench</t>
+          <t>Incline Bench</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -19537,7 +19519,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Close Grip Bench</t>
+          <t>Incline DB Bench</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -19585,9 +19567,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
@@ -19619,7 +19601,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Push-ups</t>
+          <t>Close Grip Bench</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -19701,7 +19683,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dips</t>
+          <t>Push-ups</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -19783,7 +19765,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Single-Arm DB Floor Press</t>
+          <t>Dips</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -19865,7 +19847,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Single-Arm DB Bench Press</t>
+          <t>Single-Arm DB Floor Press</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -19947,7 +19929,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Scap Push-Up</t>
+          <t>Single-Arm DB Bench Press</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -19995,9 +19977,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
@@ -20029,12 +20011,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scap Pull Ups</t>
+          <t>Scap Push-Up</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>vertical_pull</t>
+          <t>horizontal_push</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -20072,14 +20054,14 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L66" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
@@ -20092,31 +20074,31 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="O66" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="P66" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UPPER BODY — VERTICAL PUSH</t>
+          <t>UPPER BODY — HORIZONTAL PUSH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Scap Pull Ups</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vertical_push</t>
+          <t>vertical_pull</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -20154,19 +20136,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="M67" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L67" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="N67" s="6" t="inlineStr">
@@ -20174,14 +20156,14 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="O67" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="P67" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="O67" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="P67" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
     </row>
@@ -20193,7 +20175,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DB Shoulder Press</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -20275,7 +20257,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Landmine Press</t>
+          <t>DB Shoulder Press</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -20357,7 +20339,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bottoms-Up KB Press</t>
+          <t>Landmine Press</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -20439,7 +20421,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Z-Press</t>
+          <t>Bottoms-Up KB Press</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -20521,7 +20503,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Seated DB Press</t>
+          <t>Z-Press</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -20603,7 +20585,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Half-Kneeling Single-Arm Overhead Press</t>
+          <t>Seated DB Press</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -20680,17 +20662,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>UPPER BODY — HORIZONTAL PULL</t>
+          <t>UPPER BODY — VERTICAL PUSH</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Half-Kneeling Single-Arm Overhead Press</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>horizontal_pull</t>
+          <t>vertical_push</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -20728,9 +20710,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
@@ -20738,9 +20720,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="N74" s="6" t="inlineStr">
@@ -20767,7 +20749,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chest Supported Row</t>
+          <t>Barbell Row</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -20810,9 +20792,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K75" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr">
@@ -20849,7 +20831,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Chest-Supported DB Row</t>
+          <t>Chest Supported Row</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -20931,7 +20913,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Seated Cable Row</t>
+          <t>Chest-Supported DB Row</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -20974,9 +20956,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K77" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
@@ -21013,7 +20995,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Single-Arm DB Row</t>
+          <t>Seated Cable Row</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -21095,7 +21077,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Inverted Row (Bodyweight)</t>
+          <t>Single-Arm DB Row</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -21172,17 +21154,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>UPPER BODY — VERTICAL PULL</t>
+          <t>UPPER BODY — HORIZONTAL PULL</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pull-Ups</t>
+          <t>Inverted Row (Bodyweight)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>vertical_pull</t>
+          <t>horizontal_pull</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -21259,7 +21241,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Chin-Ups</t>
+          <t>Pull-Ups</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -21341,7 +21323,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lat Pulldown</t>
+          <t>Chin-Ups</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -21423,7 +21405,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Neutral-Grip Pulldown</t>
+          <t>Lat Pulldown</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -21505,7 +21487,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Single-Arm Lat Pulldown</t>
+          <t>Neutral-Grip Pulldown</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -21582,27 +21564,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>UPPER BODY — POWER / PLYO</t>
+          <t>UPPER BODY — VERTICAL PULL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Speed Trap Bar Deadlift</t>
+          <t>Single-Arm Lat Pulldown</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>hinge</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+          <t>vertical_pull</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -21610,29 +21592,29 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J85" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K85" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -21645,19 +21627,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N85" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="O85" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P85" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -21669,22 +21651,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Speed Trap Bar Deadlift</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>horizontal_push</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>hinge</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -21692,24 +21674,24 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
@@ -21717,9 +21699,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -21727,19 +21709,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N86" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="O86" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="P86" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="O86" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P86" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -21751,7 +21733,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Explosive Push-up</t>
+          <t>Speed Bench</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -21833,12 +21815,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Explosive Landmine Press</t>
+          <t>Explosive Push-up</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>vertical_push</t>
+          <t>horizontal_push</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -21881,14 +21863,14 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="L88" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="M88" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="N88" s="6" t="inlineStr">
@@ -21910,22 +21892,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CORE / TRUNK</t>
+          <t>UPPER BODY — POWER / PLYO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Band Pallof Press</t>
+          <t>Explosive Landmine Press</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+          <t>vertical_push</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -21968,9 +21950,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M89" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="N89" s="6" t="inlineStr">
@@ -21997,7 +21979,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Woodchop (Standing)</t>
+          <t>Band Pallof Press</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -22079,7 +22061,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Woodchop (Half Kneeling)</t>
+          <t>Woodchop (Standing)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -22161,7 +22143,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ab Wheel</t>
+          <t>Woodchop (Half Kneeling)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -22169,9 +22151,9 @@
           <t>core</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -22243,7 +22225,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hanging Leg Raise</t>
+          <t>Ab Wheel</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -22251,9 +22233,9 @@
           <t>core</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -22325,7 +22307,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Plank</t>
+          <t>Hanging Leg Raise</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -22407,7 +22389,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Hollow Hold</t>
+          <t>Plank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -22489,7 +22471,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Side Plank Row</t>
+          <t>Hollow Hold</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -22571,7 +22553,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Side Plank</t>
+          <t>Side Plank Row</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -22653,7 +22635,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Stir the Pot</t>
+          <t>Side Plank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -22735,7 +22717,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dragon Flag</t>
+          <t>Stir the Pot</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -22783,9 +22765,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="L99" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
@@ -22817,7 +22799,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Dead Bug</t>
+          <t>Dragon Flag</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -22865,9 +22847,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="L100" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
@@ -22899,7 +22881,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Banded Dead Bug</t>
+          <t>Dead Bug</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -22981,7 +22963,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Weighted Dead Bug</t>
+          <t>Banded Dead Bug</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -23063,7 +23045,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>McGill Sit Up</t>
+          <t>Weighted Dead Bug</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -23145,7 +23127,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bird Dog</t>
+          <t>McGill Sit Up</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -23222,17 +23204,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CARRIES</t>
+          <t>CORE / TRUNK</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Farmer Carry</t>
+          <t>Bird Dog</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>carry</t>
+          <t>core</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -23280,9 +23262,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M105" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="M105" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="N105" s="6" t="inlineStr">
@@ -23309,7 +23291,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Suitcase Carry</t>
+          <t>Farmer Carry</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -23391,7 +23373,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bear Carry</t>
+          <t>Suitcase Carry</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -23473,7 +23455,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Overhead Carry</t>
+          <t>Bear Carry</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -23550,22 +23532,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SHOULDERS / UPPER BACK</t>
+          <t>CARRIES</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lateral Raise</t>
+          <t>Overhead Carry</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>isolation_upper</t>
-        </is>
-      </c>
-      <c r="D109" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>carry</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -23598,9 +23580,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K109" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr">
@@ -23608,9 +23590,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M109" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="N109" s="6" t="inlineStr">
@@ -23637,12 +23619,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Face Pull</t>
+          <t>Lateral Raise</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>horizontal_pull</t>
+          <t>isolation_upper</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -23719,7 +23701,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cable Face Pull</t>
+          <t>Face Pull</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -23801,7 +23783,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Rear Delt Fly</t>
+          <t>Cable Face Pull</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -23883,7 +23865,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Band Pull-Apart</t>
+          <t>Rear Delt Fly</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -23965,12 +23947,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Banded External Rotation</t>
+          <t>Band Pull-Apart</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>isolation_upper</t>
+          <t>horizontal_pull</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -24047,7 +24029,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Shrugs</t>
+          <t>Banded External Rotation</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -24100,9 +24082,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M115" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="M115" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="N115" s="6" t="inlineStr">
@@ -24129,7 +24111,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Single-Arm Shrug</t>
+          <t>Shrugs</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -24182,9 +24164,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M116" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="M116" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="N116" s="6" t="inlineStr">
@@ -24211,7 +24193,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Incline Y Raise</t>
+          <t>Single-Arm Shrug</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -24254,9 +24236,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K117" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
@@ -24288,12 +24270,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ARMS — BICEPS</t>
+          <t>SHOULDERS / UPPER BACK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bicep Curl (Barbell)</t>
+          <t>Incline Y Raise</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -24336,9 +24318,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K118" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="K118" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">
@@ -24375,7 +24357,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bicep Curl (Dumbbell)</t>
+          <t>Bicep Curl (Barbell)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -24457,7 +24439,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Hammer Curl</t>
+          <t>Bicep Curl (Dumbbell)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -24539,12 +24521,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Chin-Up Negative (Slow)</t>
+          <t>Hammer Curl</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>vertical_pull</t>
+          <t>isolation_upper</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -24621,12 +24603,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Incline Dumbbell Curl</t>
+          <t>Chin-Up Negative (Slow)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>isolation_upper</t>
+          <t>vertical_pull</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -24703,7 +24685,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Lying Dumbbell Curl</t>
+          <t>Incline Dumbbell Curl</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -24785,7 +24767,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Banded Bicep Curl</t>
+          <t>Lying Dumbbell Curl</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -24867,7 +24849,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Concentration Curl</t>
+          <t>Banded Bicep Curl</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -24944,12 +24926,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ARMS — TRICEPS</t>
+          <t>ARMS — BICEPS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tricep Pushdown</t>
+          <t>Concentration Curl</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -25031,7 +25013,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Banded Tricep Pushdown</t>
+          <t>Tricep Pushdown</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -25113,7 +25095,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Skull Crushers</t>
+          <t>Banded Tricep Pushdown</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -25195,7 +25177,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dumbbell Skull Crusher</t>
+          <t>Skull Crushers</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -25277,7 +25259,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Overhead Tricep Extension</t>
+          <t>Dumbbell Skull Crusher</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -25359,7 +25341,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dumbbell Kickback</t>
+          <t>Overhead Tricep Extension</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -25441,7 +25423,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tricep Circuit (Dirty 30)</t>
+          <t>Dumbbell Kickback</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -25518,82 +25500,82 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>INTAKE (after 2026-07-28)</t>
+          <t>ARMS — TRICEPS</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Rotational Medicine-Ball Slam</t>
+          <t>Tricep Circuit (Dirty 30)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E133" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="F133" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="G133" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="H133" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="I133" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="J133" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="K133" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="L133" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="M133" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="N133" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="O133" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P133" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+          <t>isolation_upper</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="M133" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N133" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="O133" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="P133" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -25605,17 +25587,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Medicine-Ball Slam</t>
+          <t>Rotational Medicine-Ball Slam</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>vertical_pull</t>
-        </is>
-      </c>
-      <c r="D134" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="E134" s="10" t="inlineStr">
@@ -25668,9 +25650,9 @@
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="O134" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="O134" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="P134" s="9" t="inlineStr">
@@ -25687,17 +25669,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Rotational Medicine-Ball Throw</t>
+          <t>Medicine-Ball Slam</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+          <t>vertical_pull</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="E135" s="10" t="inlineStr">
@@ -25750,14 +25732,14 @@
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="O135" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P135" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="O135" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="P135" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
     </row>
@@ -25769,12 +25751,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Reverse Nordic Curl</t>
+          <t>Rotational Medicine-Ball Throw</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
+          <t>core</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -25782,64 +25764,64 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F136" s="9" t="inlineStr">
+      <c r="E136" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="J136" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="K136" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="G136" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="H136" s="9" t="inlineStr">
+      <c r="L136" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="I136" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="J136" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K136" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L136" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="M136" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N136" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O136" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P136" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="M136" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="N136" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="O136" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P136" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25833,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SL 45° Back Extension Hold</t>
+          <t>Reverse Nordic Curl</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -25869,24 +25851,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="G137" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="G137" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H137" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="I137" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
@@ -25894,9 +25876,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="K137" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr">
@@ -25909,19 +25891,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N137" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="O137" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P137" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O137" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="P137" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -25933,12 +25915,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SL 45° Back Extension</t>
+          <t>SL 45° Back Extension Hold</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>hinge</t>
+          <t>isolation_lower</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -25951,9 +25933,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="G138" s="6" t="inlineStr">
@@ -25961,24 +25943,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="H138" s="10" t="inlineStr">
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K138" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="I138" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="J138" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="K138" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr">
@@ -26015,7 +25997,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Seated Good Morning</t>
+          <t>SL 45° Back Extension</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -26048,14 +26030,14 @@
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="I139" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="J139" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
@@ -26068,9 +26050,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M139" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="M139" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="N139" s="10" t="inlineStr">
@@ -26097,77 +26079,77 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Crab Hold</t>
+          <t>Seated Good Morning</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="D140" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="E140" s="10" t="inlineStr">
+          <t>hinge</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G140" s="10" t="inlineStr">
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L140" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="M140" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="H140" s="10" t="inlineStr">
+      <c r="N140" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="I140" s="10" t="inlineStr">
+      <c r="O140" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="J140" s="10" t="inlineStr">
+      <c r="P140" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="K140" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="L140" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="M140" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="N140" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="O140" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P140" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
         </is>
       </c>
     </row>
@@ -26179,52 +26161,52 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Standing Knee Extension</t>
+          <t>Crab Hold</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H141" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J141" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="E141" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G141" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="H141" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="I141" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="J141" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="K141" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr">
@@ -26232,24 +26214,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M141" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N141" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O141" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P141" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="M141" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="N141" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="O141" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P141" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
     </row>
@@ -26261,7 +26243,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Seated Single-Leg Pike Lift</t>
+          <t>Standing Knee Extension</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -26289,19 +26271,19 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="H142" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="I142" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="J142" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="K142" s="4" t="inlineStr">
@@ -26343,7 +26325,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Horse Stance Hold</t>
+          <t>Seated Single-Leg Pike Lift</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -26366,24 +26348,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="G143" s="10" t="inlineStr">
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H143" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
       <c r="I143" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="J143" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="J143" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -26425,52 +26407,52 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Bench Thoracic Extension</t>
+          <t>Horse Stance Hold</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="D144" s="10" t="inlineStr">
+          <t>isolation_lower</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G144" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G144" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H144" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J144" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="K144" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I144" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr">
@@ -26478,19 +26460,19 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M144" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="N144" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="O144" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="M144" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
@@ -26507,17 +26489,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Sleeper Stretch</t>
+          <t>Bench Thoracic Extension</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>isolation_upper</t>
-        </is>
-      </c>
-      <c r="D145" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -26535,9 +26517,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="H145" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
@@ -26545,19 +26527,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K145" s="10" t="inlineStr">
+      <c r="J145" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="L145" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M145" s="10" t="inlineStr">
@@ -26570,14 +26552,14 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="O145" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="P145" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="O145" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P145" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -26589,59 +26571,59 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Foam Roller Thoracic Extension</t>
+          <t>Sleeper Stretch</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="D146" s="10" t="inlineStr">
+          <t>isolation_upper</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K146" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="L146" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G146" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H146" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K146" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="L146" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
@@ -26652,14 +26634,14 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="O146" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P146" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="O146" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="P146" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -26671,52 +26653,52 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Hip 90/90 Stretch</t>
+          <t>Foam Roller Thoracic Extension</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E147" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="F147" s="10" t="inlineStr">
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="G147" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="H147" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="I147" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="J147" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="K147" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr">
@@ -26724,24 +26706,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M147" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N147" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O147" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P147" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="M147" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="N147" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="O147" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P147" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -26753,77 +26735,77 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Cat-Cow</t>
+          <t>Hip 90/90 Stretch</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="D148" s="10" t="inlineStr">
+          <t>isolation_lower</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="F148" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G148" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H148" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="G148" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr">
         <is>
-          <t>caution (exc)</t>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="J148" s="10" t="inlineStr">
         <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="K148" s="10" t="inlineStr">
-        <is>
           <t>good (exc)</t>
         </is>
       </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
       <c r="L148" s="6" t="inlineStr">
         <is>
           <t>caution</t>
         </is>
       </c>
-      <c r="M148" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="N148" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="O148" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="P148" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="M148" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="P148" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -26835,52 +26817,52 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>World's Greatest Stretch</t>
+          <t>Cat-Cow</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F149" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G149" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H149" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J149" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K149" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H149" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="I149" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="J149" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="K149" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr">
@@ -26888,24 +26870,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M149" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N149" s="10" t="inlineStr">
+      <c r="M149" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="O149" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P149" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="N149" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="O149" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="P149" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -26917,7 +26899,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Deep Squat Hold</t>
+          <t>World's Greatest Stretch</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -26940,14 +26922,14 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="G150" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="H150" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="I150" s="6" t="inlineStr">
@@ -26955,9 +26937,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="J150" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="J150" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr">
@@ -26975,19 +26957,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N150" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O150" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P150" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N150" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="O150" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P150" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -26999,7 +26981,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Couch Stretch</t>
+          <t>Deep Squat Hold</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -27007,39 +26989,39 @@
           <t>isolation_lower</t>
         </is>
       </c>
-      <c r="D151" s="10" t="inlineStr">
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G151" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E151" s="9" t="inlineStr">
+      <c r="H151" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="F151" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G151" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="H151" s="9" t="inlineStr">
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="I151" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="J151" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
@@ -27081,12 +27063,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Open Book Thoracic Rotation</t>
+          <t>Couch Stretch</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>isolation_lower</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
@@ -27094,39 +27076,39 @@
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I152" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K152" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="E152" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="H152" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="I152" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L152" s="6" t="inlineStr">
@@ -27134,24 +27116,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M152" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="N152" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="O152" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="P152" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="M152" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="P152" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -27163,77 +27145,77 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Pigeon Stretch</t>
+          <t>Open Book Thoracic Rotation</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E153" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="F153" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G153" s="10" t="inlineStr">
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="H153" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="I153" s="10" t="inlineStr">
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L153" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="M153" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="N153" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="O153" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="J153" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K153" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L153" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="M153" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N153" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O153" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
       <c r="P153" s="10" t="inlineStr">
         <is>
-          <t>caution (exc)</t>
+          <t>good (exc)</t>
         </is>
       </c>
     </row>
@@ -27245,7 +27227,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Adductor Rockback</t>
+          <t>Pigeon Stretch</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -27253,36 +27235,36 @@
           <t>isolation_lower</t>
         </is>
       </c>
-      <c r="D154" s="9" t="inlineStr">
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E154" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F154" s="10" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="G154" s="10" t="inlineStr">
+      <c r="H154" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="I154" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I154" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
       <c r="J154" s="6" t="inlineStr">
         <is>
           <t>caution</t>
@@ -27303,14 +27285,14 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N154" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="O154" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="P154" s="10" t="inlineStr">
@@ -27327,77 +27309,77 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chest / Pec Stretch (Doorway)</t>
+          <t>Adductor Rockback</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>isolation_upper</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K155" s="10" t="inlineStr">
+          <t>isolation_lower</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F155" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="G155" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I155" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L155" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="M155" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N155" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="L155" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="M155" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N155" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="O155" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="O155" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="P155" s="10" t="inlineStr">
         <is>
-          <t>good (exc)</t>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -27409,7 +27391,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Lat Stretch</t>
+          <t>Chest / Pec Stretch (Doorway)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -27457,9 +27439,9 @@
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="L156" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="L156" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
@@ -27477,9 +27459,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="P156" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="P156" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
     </row>
@@ -27491,7 +27473,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dead Hang</t>
+          <t>Lat Stretch</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -27539,9 +27521,9 @@
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="L157" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="L157" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
@@ -27554,9 +27536,9 @@
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="O157" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="O157" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="P157" s="6" t="inlineStr">
@@ -27573,77 +27555,77 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Toe Stretch</t>
+          <t>Dead Hang</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
-        </is>
-      </c>
-      <c r="D158" s="10" t="inlineStr">
+          <t>isolation_upper</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K158" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="L158" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E158" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="F158" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="G158" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="H158" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J158" s="9" t="inlineStr">
+      <c r="M158" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N158" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="K158" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L158" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="M158" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N158" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O158" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P158" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="O158" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="P158" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -27655,7 +27637,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Calf Stretch</t>
+          <t>Toe Stretch</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -27678,9 +27660,9 @@
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="G159" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="G159" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
@@ -27688,9 +27670,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="I159" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="J159" s="9" t="inlineStr">
@@ -27737,12 +27719,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>QL Back Extension</t>
+          <t>Calf Stretch</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>isolation_lower</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
@@ -27752,62 +27734,62 @@
       </c>
       <c r="E160" s="10" t="inlineStr">
         <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G160" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J160" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="K160" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="L160" s="9" t="inlineStr">
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="F160" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I160" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
+      <c r="J160" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L160" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N160" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="O160" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="P160" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="P160" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -27819,77 +27801,77 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ATG Split Squat</t>
+          <t>QL Back Extension</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E161" s="9" t="inlineStr">
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="E161" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G161" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J161" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L161" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H161" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J161" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K161" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L161" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N161" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O161" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P161" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N161" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="O161" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="P161" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
     </row>
@@ -27901,7 +27883,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Elephant Walks</t>
+          <t>ATG Split Squat</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -27909,29 +27891,29 @@
           <t>isolation_lower</t>
         </is>
       </c>
-      <c r="D162" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F162" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="G162" s="9" t="inlineStr">
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="H162" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="I162" s="6" t="inlineStr">
@@ -27939,9 +27921,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="J162" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="J162" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr">
@@ -27949,9 +27931,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="L162" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="L162" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
@@ -27969,9 +27951,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="P162" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="P162" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -27983,7 +27965,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Butterfly Stretch</t>
+          <t>Elephant Walks</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -27991,51 +27973,51 @@
           <t>isolation_lower</t>
         </is>
       </c>
-      <c r="D163" s="9" t="inlineStr">
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F163" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="G163" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="E163" s="9" t="inlineStr">
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J163" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L163" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="F163" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="G163" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="H163" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="I163" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="J163" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="K163" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L163" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
           <t>good (dec)</t>
@@ -28051,9 +28033,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="P163" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="P163" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -28065,7 +28047,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Pissing Dog Against Wall</t>
+          <t>Butterfly Stretch</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -28073,9 +28055,9 @@
           <t>isolation_lower</t>
         </is>
       </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="D164" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="E164" s="9" t="inlineStr">
@@ -28093,9 +28075,9 @@
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="H164" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr">
@@ -28103,9 +28085,9 @@
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="J164" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="J164" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr">
@@ -28113,9 +28095,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="L164" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
+      <c r="L164" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
@@ -28123,19 +28105,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N164" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="O164" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P164" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O164" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="P164" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -28147,77 +28129,77 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Jefferson Curl</t>
+          <t>Pissing Dog Against Wall</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="D165" s="10" t="inlineStr">
+          <t>isolation_lower</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="F165" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E165" s="10" t="inlineStr">
+      <c r="G165" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I165" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L165" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="M165" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N165" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G165" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="H165" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I165" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J165" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="K165" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="L165" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="M165" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="N165" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="O165" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="P165" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="O165" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P165" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -28229,22 +28211,22 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dumbbell Pullovers</t>
+          <t>Jefferson Curl</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>isolation_upper</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="E166" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -28252,9 +28234,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="G166" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -28262,34 +28244,34 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="I166" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K166" s="9" t="inlineStr">
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J166" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L166" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
         </is>
       </c>
-      <c r="L166" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="M166" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N166" s="9" t="inlineStr">
+      <c r="M166" s="9" t="inlineStr">
         <is>
           <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="N166" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="O166" s="6" t="inlineStr">
@@ -28311,52 +28293,52 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Foam Roll — Hip Flexor, Quad, Adductors</t>
+          <t>Dumbbell Pullovers</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E167" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F167" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G167" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="H167" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I167" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="J167" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="K167" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>isolation_upper</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K167" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr">
@@ -28369,19 +28351,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N167" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="O167" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P167" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N167" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="O167" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="P167" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -28393,52 +28375,52 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Foam Roll — T-Spine</t>
+          <t>Foam Roll — Hip Flexor, Quad, Adductors</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="D168" s="10" t="inlineStr">
+          <t>isolation_lower</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G168" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I168" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K168" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I168" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="J168" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L168" s="6" t="inlineStr">
@@ -28446,24 +28428,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="M168" s="10" t="inlineStr">
+      <c r="M168" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N168" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="N168" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
       <c r="O168" s="10" t="inlineStr">
         <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="P168" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P168" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -28475,12 +28457,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Foam Roll — IT Band</t>
+          <t>Foam Roll — T-Spine</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
+          <t>core</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
@@ -28488,64 +28470,64 @@
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F169" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G169" s="10" t="inlineStr">
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K169" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L169" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="M169" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="N169" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="H169" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I169" s="10" t="inlineStr">
+      <c r="O169" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="J169" s="10" t="inlineStr">
+      <c r="P169" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="K169" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L169" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="M169" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N169" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="O169" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P169" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -28557,77 +28539,77 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Foam Roll — Lats</t>
+          <t>Foam Roll — IT Band</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>isolation_upper</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K170" s="10" t="inlineStr">
+          <t>isolation_lower</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G170" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I170" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="J170" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L170" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="M170" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N170" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="L170" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="M170" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N170" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
       <c r="O170" s="10" t="inlineStr">
         <is>
-          <t>good (exc)</t>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="P170" s="10" t="inlineStr">
         <is>
-          <t>good (exc)</t>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -28639,77 +28621,77 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Foam Roll — Calves &amp; Outer Shins</t>
+          <t>Foam Roll — Lats</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
-        </is>
-      </c>
-      <c r="D171" s="10" t="inlineStr">
+          <t>isolation_upper</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K171" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="L171" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E171" s="10" t="inlineStr">
+      <c r="M171" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N171" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="O171" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="F171" s="10" t="inlineStr">
+      <c r="P171" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="G171" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="H171" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="I171" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J171" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K171" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L171" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="M171" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="N171" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="O171" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="P171" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -28721,7 +28703,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Lacrosse Ball Glute Release</t>
+          <t>Foam Roll — Calves &amp; Outer Shins</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -28734,9 +28716,9 @@
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="E172" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="F172" s="10" t="inlineStr">
@@ -28754,24 +28736,24 @@
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="I172" s="10" t="inlineStr">
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J172" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L172" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="J172" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="K172" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L172" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr">
@@ -28803,12 +28785,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>90/90 Breathing</t>
+          <t>Lacrosse Ball Glute Release</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>isolation_lower</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
@@ -28816,64 +28798,64 @@
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I173" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J173" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K173" s="10" t="inlineStr">
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F173" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="L173" s="10" t="inlineStr">
+      <c r="G173" s="10" t="inlineStr">
         <is>
           <t>good (exc)</t>
         </is>
       </c>
+      <c r="H173" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="I173" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="J173" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L173" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
       <c r="M173" s="4" t="inlineStr">
         <is>
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N173" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
-        </is>
-      </c>
-      <c r="O173" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P173" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O173" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="P173" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
@@ -28885,7 +28867,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Crocodile Breathing</t>
+          <t>90/90 Breathing</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -28928,9 +28910,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K174" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="K174" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="L174" s="10" t="inlineStr">
@@ -28967,7 +28949,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Box Breathing</t>
+          <t>Crocodile Breathing</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -29010,9 +28992,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="K175" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="K175" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L175" s="10" t="inlineStr">
@@ -29049,7 +29031,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Child's Pose with Breathing</t>
+          <t>Box Breathing</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -29062,9 +29044,9 @@
           <t>good (exc)</t>
         </is>
       </c>
-      <c r="E176" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -29077,9 +29059,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="H176" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="I176" s="4" t="inlineStr">
@@ -29087,9 +29069,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="J176" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="K176" s="10" t="inlineStr">
@@ -29107,9 +29089,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N176" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="N176" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="O176" s="4" t="inlineStr">
@@ -29131,57 +29113,57 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>T-Bar Tib Raises</t>
+          <t>Child's Pose with Breathing</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>isolation_lower</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F177" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G177" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H177" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I177" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J177" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K177" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L177" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="E177" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H177" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J177" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="K177" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="L177" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
@@ -29189,9 +29171,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N177" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N177" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="O177" s="4" t="inlineStr">
@@ -29213,12 +29195,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Single-Leg Hop and Stick</t>
+          <t>T-Bar Tib Raises</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>plyo</t>
+          <t>isolation_lower</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
@@ -29241,24 +29223,24 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="H178" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="I178" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="J178" s="9" t="inlineStr">
-        <is>
-          <t>avoid (exc)</t>
-        </is>
-      </c>
-      <c r="K178" s="10" t="inlineStr">
-        <is>
-          <t>good (exc)</t>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L178" s="6" t="inlineStr">
@@ -29295,77 +29277,77 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Incline Push-Up</t>
+          <t>Single-Leg Hop and Stick</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>horizontal_push</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I179" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J179" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="K179" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="L179" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="M179" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
-      <c r="N179" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="O179" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="P179" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+          <t>plyo</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H179" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="I179" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="inlineStr">
+        <is>
+          <t>avoid (exc)</t>
+        </is>
+      </c>
+      <c r="K179" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="M179" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="N179" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="O179" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="P179" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -29377,12 +29359,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Band-Assisted Pull-Up</t>
+          <t>Incline Push-Up</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>vertical_pull</t>
+          <t>horizontal_push</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -29420,21 +29402,21 @@
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="K180" s="10" t="inlineStr">
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L180" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="L180" s="10" t="inlineStr">
+      <c r="M180" s="10" t="inlineStr">
         <is>
           <t>caution (exc)</t>
         </is>
       </c>
-      <c r="M180" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
-        </is>
-      </c>
       <c r="N180" s="6" t="inlineStr">
         <is>
           <t>caution</t>
@@ -29445,9 +29427,9 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="P180" s="10" t="inlineStr">
-        <is>
-          <t>caution (exc)</t>
+      <c r="P180" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -29459,12 +29441,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Banded 90/90 External Rotation</t>
+          <t>Band-Assisted Pull-Up</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>isolation_upper</t>
+          <t>vertical_pull</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -29497,19 +29479,19 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="J181" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K181" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="J181" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
+        </is>
+      </c>
+      <c r="K181" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="L181" s="10" t="inlineStr">
         <is>
-          <t>good (exc)</t>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="M181" s="10" t="inlineStr">
@@ -29527,76 +29509,76 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="P181" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="P181" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CONDITIONING</t>
+          <t>INTAKE (after 2026-07-28)</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Sprint Intervals</t>
+          <t>Banded 90/90 External Rotation</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>conditioning</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G182" s="9" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I182" s="9" t="inlineStr">
-        <is>
-          <t>avoid</t>
-        </is>
-      </c>
-      <c r="J182" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K182" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="M182" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+          <t>isolation_upper</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L182" s="10" t="inlineStr">
+        <is>
+          <t>good (exc)</t>
+        </is>
+      </c>
+      <c r="M182" s="10" t="inlineStr">
+        <is>
+          <t>caution (exc)</t>
         </is>
       </c>
       <c r="N182" s="6" t="inlineStr">
@@ -29604,14 +29586,14 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="O182" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="P182" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="O182" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="P182" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -29623,7 +29605,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hill Sprints</t>
+          <t>Sprint Intervals</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -29705,7 +29687,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Quality Sprints</t>
+          <t>Hill Sprints</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -29787,7 +29769,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MAS Training</t>
+          <t>Quality Sprints</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -29869,7 +29851,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MetCon</t>
+          <t>MAS Training</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -29877,49 +29859,49 @@
           <t>conditioning</t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J186" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K186" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L186" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G186" s="9" t="inlineStr">
+        <is>
+          <t>avoid</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I186" s="9" t="inlineStr">
+        <is>
+          <t>avoid</t>
+        </is>
+      </c>
+      <c r="J186" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L186" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
@@ -29951,7 +29933,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Long Run</t>
+          <t>MetCon</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -29959,49 +29941,49 @@
           <t>conditioning</t>
         </is>
       </c>
-      <c r="D187" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E187" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H187" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I187" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J187" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K187" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="L187" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F187" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="L187" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
@@ -30009,9 +29991,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N187" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N187" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="O187" s="4" t="inlineStr">
@@ -30033,7 +30015,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>6x1km</t>
+          <t>Long Run</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -30115,7 +30097,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Hard Row Intervals</t>
+          <t>6x1km</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -30123,49 +30105,49 @@
           <t>conditioning</t>
         </is>
       </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F189" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G189" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H189" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J189" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K189" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="L189" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J189" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
@@ -30173,9 +30155,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N189" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="O189" s="4" t="inlineStr">
@@ -30183,9 +30165,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="P189" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="P189" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -30197,7 +30179,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Hard SkiErg Intervals</t>
+          <t>Hard Row Intervals</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -30279,7 +30261,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Hard Assault Bike Intervals</t>
+          <t>Hard SkiErg Intervals</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -30307,9 +30289,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="H191" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="H191" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="I191" s="4" t="inlineStr">
@@ -30327,9 +30309,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="L191" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="L191" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M191" s="4" t="inlineStr">
@@ -30347,9 +30329,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="P191" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="P191" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -30361,7 +30343,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Tempo Run</t>
+          <t>Hard Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -30369,24 +30351,24 @@
           <t>conditioning</t>
         </is>
       </c>
-      <c r="D192" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E192" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G192" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E192" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F192" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G192" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="H192" s="6" t="inlineStr">
@@ -30394,19 +30376,19 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="I192" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J192" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K192" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K192" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L192" s="4" t="inlineStr">
@@ -30419,9 +30401,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N192" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N192" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="O192" s="4" t="inlineStr">
@@ -30443,7 +30425,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Air Bike Sprints</t>
+          <t>Tempo Run</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -30451,24 +30433,24 @@
           <t>conditioning</t>
         </is>
       </c>
-      <c r="D193" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F193" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G193" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="H193" s="6" t="inlineStr">
@@ -30476,19 +30458,19 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="I193" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J193" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K193" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L193" s="4" t="inlineStr">
@@ -30501,9 +30483,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N193" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="N193" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="O193" s="4" t="inlineStr">
@@ -30525,7 +30507,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Row Intervals</t>
+          <t>Air Bike Sprints</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -30553,9 +30535,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="H194" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="I194" s="4" t="inlineStr">
@@ -30573,9 +30555,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="L194" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="L194" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
@@ -30593,9 +30575,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="P194" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="P194" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -30607,7 +30589,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SkiErg Intervals</t>
+          <t>Row Intervals</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -30689,7 +30671,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Assault Bike Intervals</t>
+          <t>SkiErg Intervals</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -30717,9 +30699,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="H196" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="H196" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="I196" s="4" t="inlineStr">
@@ -30737,9 +30719,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="L196" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="L196" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr">
@@ -30757,9 +30739,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="P196" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="P196" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -30771,7 +30753,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Flush Run</t>
+          <t>Assault Bike Intervals</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -30779,24 +30761,24 @@
           <t>conditioning</t>
         </is>
       </c>
-      <c r="D197" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E197" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F197" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G197" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="H197" s="6" t="inlineStr">
@@ -30804,19 +30786,19 @@
           <t>caution</t>
         </is>
       </c>
-      <c r="I197" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J197" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K197" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L197" s="4" t="inlineStr">
@@ -30829,9 +30811,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N197" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N197" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="O197" s="4" t="inlineStr">
@@ -30853,7 +30835,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Easy Bike</t>
+          <t>Flush Run</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -30861,44 +30843,44 @@
           <t>conditioning</t>
         </is>
       </c>
-      <c r="D198" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="F198" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="G198" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="H198" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="J198" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
-        </is>
-      </c>
-      <c r="K198" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J198" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="L198" s="4" t="inlineStr">
@@ -30935,7 +30917,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Easy Row</t>
+          <t>Easy Bike</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -30983,9 +30965,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="L199" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="L199" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr">
@@ -30993,9 +30975,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N199" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="O199" s="4" t="inlineStr">
@@ -31003,9 +30985,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="P199" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="P199" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -31017,7 +30999,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Easy Ski</t>
+          <t>Easy Row</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -31099,7 +31081,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Easy Swim</t>
+          <t>Easy Ski</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -31147,9 +31129,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="L201" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="L201" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="M201" s="4" t="inlineStr">
@@ -31167,9 +31149,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="P201" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="P201" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
     </row>
@@ -31181,7 +31163,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Light Circuits</t>
+          <t>Easy Swim</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -31239,9 +31221,9 @@
           <t>good (dec)</t>
         </is>
       </c>
-      <c r="N202" s="4" t="inlineStr">
-        <is>
-          <t>good (dec)</t>
+      <c r="N202" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
         </is>
       </c>
       <c r="O202" s="4" t="inlineStr">
@@ -31258,12 +31240,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>INTAKE (after 2026-07-28)</t>
+          <t>CONDITIONING</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Light Walk or Stationary Bike</t>
+          <t>Light Circuits</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -31271,69 +31253,69 @@
           <t>conditioning</t>
         </is>
       </c>
-      <c r="D203" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E203" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F203" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G203" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H203" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I203" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J203" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
+        </is>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="K203" s="4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="M203" s="4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="N203" s="4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="O203" s="4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>good (dec)</t>
         </is>
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>good (dec)</t>
         </is>
       </c>
     </row>
@@ -31345,7 +31327,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Incline Treadmill Walk</t>
+          <t>Light Walk or Stationary Bike</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -31427,75 +31409,157 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
+          <t>Incline Treadmill Walk</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>conditioning</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J205" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L205" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M205" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N205" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O205" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P205" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>INTAKE (after 2026-07-28)</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
           <t>Outdoor Walk</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>conditioning</t>
         </is>
       </c>
-      <c r="D205" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="E205" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="F205" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="G205" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="H205" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="I205" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="J205" s="6" t="inlineStr">
-        <is>
-          <t>caution</t>
-        </is>
-      </c>
-      <c r="K205" s="4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="L205" s="4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="M205" s="4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="N205" s="4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="O205" s="4" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="P205" s="4" t="inlineStr">
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="inlineStr">
+        <is>
+          <t>caution</t>
+        </is>
+      </c>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="L206" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="M206" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="N206" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="O206" s="4" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="P206" s="4" t="inlineStr">
         <is>
           <t>good</t>
         </is>

--- a/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
+++ b/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
@@ -20749,7 +20749,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Bent Row</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">

--- a/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
+++ b/docs/INJURY_MATRIX_REVIEW_2026-07-28.xlsx
@@ -16674,7 +16674,7 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
